--- a/ASTquizApp/qBanks/OFC.xlsx
+++ b/ASTquizApp/qBanks/OFC.xlsx
@@ -1,23 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programDo\vs\ASTquizApp\ASTquizApp\qBanks\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D240EE8E-6A7A-4EDC-AA83-E22DFE4B9135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="12240" windowHeight="8010" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="OFC Jointing Course" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OFC Jointing Course'!$A$1:$O$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$114</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="440" count="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="440">
   <si>
     <t>Question</t>
   </si>
@@ -1342,52 +1348,46 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="49" formatCode="@"/>
-    <numFmt numFmtId="9" formatCode="0%"/>
-    <numFmt numFmtId="10" formatCode="0.00%"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="7"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="Arial"/>
-      <sz val="12"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1446,29 +1446,22 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="bottom"/>
-      <protection locked="0" hidden="0"/>
+      <protection locked="0"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1479,12 +1472,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1494,26 +1487,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1523,27 +1514,43 @@
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1584,35 +1591,23 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16" count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1650,7 +1645,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1684,6 +1679,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1718,9 +1714,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1826,7 +1823,7 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
+            <a:lightRig rig="threePt" dir="t">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
@@ -1893,29 +1890,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P230"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O230"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" hidden="1" customWidth="1" width="17.140625" style="1"/>
-    <col min="2" max="2" hidden="1" customWidth="1" bestFit="1" width="22.140625" style="1"/>
-    <col min="3" max="3" hidden="1" customWidth="1" bestFit="1" width="5.140625" style="2"/>
-    <col min="4" max="4" hidden="1" customWidth="1" bestFit="1" width="26.425781" style="1"/>
-    <col min="5" max="5" hidden="1" customWidth="1" width="5.2851562" style="3"/>
-    <col min="6" max="6" hidden="1" customWidth="1" bestFit="1" width="8.425781" style="3"/>
-    <col min="7" max="7" customWidth="1" bestFit="1" width="6.7109375" style="3"/>
-    <col min="8" max="8" customWidth="1" bestFit="1" width="55.570312" style="1"/>
-    <col min="9" max="9" customWidth="1" bestFit="1" width="19.285156" style="1"/>
-    <col min="10" max="10" customWidth="1" bestFit="1" width="22.855469" style="1"/>
-    <col min="11" max="11" customWidth="1" bestFit="1" width="19.570312" style="1"/>
-    <col min="12" max="12" customWidth="1" bestFit="1" width="20.285156" style="1"/>
-    <col min="13" max="13" customWidth="1" width="9.425781" style="1"/>
-    <col min="14" max="14" hidden="1" customWidth="1" width="9.425781" style="3"/>
-    <col min="15" max="15" hidden="1" customWidth="1" width="12.285156" style="3"/>
-    <col min="16" max="16384" customWidth="0" width="9.140625" style="1"/>
+    <col min="1" max="1" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="55.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" style="3" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" style="3" hidden="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:8" s="4" ht="18.75" customFormat="1">
+    <row r="1" spans="1:15" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>366</v>
       </c>
@@ -1962,7 +1959,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="2" spans="8:8" ht="60.0">
+    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>375</v>
       </c>
@@ -1970,7 +1967,7 @@
         <v>376</v>
       </c>
       <c r="C2" s="7">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>370</v>
@@ -1979,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>369</v>
@@ -2003,13 +2000,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="10">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O2" s="11" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="3" spans="8:8" ht="60.0">
+    <row r="3" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>375</v>
       </c>
@@ -2017,7 +2014,7 @@
         <v>376</v>
       </c>
       <c r="C3" s="12">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>370</v>
@@ -2026,7 +2023,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>369</v>
@@ -2035,28 +2032,28 @@
         <v>10</v>
       </c>
       <c r="I3" s="12">
-        <v>1966.0</v>
+        <v>1966</v>
       </c>
       <c r="J3" s="12">
-        <v>1927.0</v>
+        <v>1927</v>
       </c>
       <c r="K3" s="12">
-        <v>1980.0</v>
+        <v>1980</v>
       </c>
       <c r="L3" s="12">
-        <v>1880.0</v>
+        <v>1880</v>
       </c>
       <c r="M3" s="12" t="s">
         <v>3</v>
       </c>
       <c r="N3" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O3" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="4" spans="8:8" ht="60.0">
+    <row r="4" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>375</v>
       </c>
@@ -2064,7 +2061,7 @@
         <v>376</v>
       </c>
       <c r="C4" s="12">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>370</v>
@@ -2073,7 +2070,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>369</v>
@@ -2097,13 +2094,13 @@
         <v>3</v>
       </c>
       <c r="N4" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O4" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="5" spans="8:8" ht="60.0">
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>375</v>
       </c>
@@ -2111,7 +2108,7 @@
         <v>376</v>
       </c>
       <c r="C5" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>370</v>
@@ -2120,7 +2117,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>369</v>
@@ -2129,28 +2126,28 @@
         <v>16</v>
       </c>
       <c r="I5" s="17">
-        <v>1927.0</v>
+        <v>1927</v>
       </c>
       <c r="J5" s="17">
-        <v>1960.0</v>
+        <v>1960</v>
       </c>
       <c r="K5" s="17">
-        <v>1970.0</v>
+        <v>1970</v>
       </c>
       <c r="L5" s="17">
-        <v>1980.0</v>
+        <v>1980</v>
       </c>
       <c r="M5" s="17" t="s">
         <v>2</v>
       </c>
       <c r="N5" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O5" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="6" spans="8:8" ht="60.0">
+    <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>375</v>
       </c>
@@ -2158,7 +2155,7 @@
         <v>376</v>
       </c>
       <c r="C6" s="12">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>370</v>
@@ -2167,7 +2164,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>369</v>
@@ -2191,13 +2188,13 @@
         <v>4</v>
       </c>
       <c r="N6" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O6" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="7" spans="8:8" ht="60.0">
+    <row r="7" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>375</v>
       </c>
@@ -2205,7 +2202,7 @@
         <v>376</v>
       </c>
       <c r="C7" s="12">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>371</v>
@@ -2214,7 +2211,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>369</v>
@@ -2223,28 +2220,28 @@
         <v>22</v>
       </c>
       <c r="I7" s="17">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="17">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K7" s="17">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L7" s="17">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="M7" s="12" t="s">
         <v>2</v>
       </c>
       <c r="N7" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O7" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="8" spans="8:8" ht="60.0">
+    <row r="8" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>375</v>
       </c>
@@ -2252,7 +2249,7 @@
         <v>376</v>
       </c>
       <c r="C8" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>371</v>
@@ -2261,7 +2258,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>369</v>
@@ -2285,13 +2282,13 @@
         <v>3</v>
       </c>
       <c r="N8" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O8" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="9" spans="8:8" ht="60.0">
+    <row r="9" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>375</v>
       </c>
@@ -2299,7 +2296,7 @@
         <v>376</v>
       </c>
       <c r="C9" s="12">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>371</v>
@@ -2308,7 +2305,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>369</v>
@@ -2332,13 +2329,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O9" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="10" spans="8:8" ht="60.0">
+    <row r="10" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>375</v>
       </c>
@@ -2346,7 +2343,7 @@
         <v>376</v>
       </c>
       <c r="C10" s="12">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>371</v>
@@ -2355,7 +2352,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>369</v>
@@ -2379,13 +2376,13 @@
         <v>4</v>
       </c>
       <c r="N10" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O10" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="11" spans="8:8" ht="60.0">
+    <row r="11" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>375</v>
       </c>
@@ -2393,7 +2390,7 @@
         <v>376</v>
       </c>
       <c r="C11" s="7">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>371</v>
@@ -2402,7 +2399,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>369</v>
@@ -2426,13 +2423,13 @@
         <v>4</v>
       </c>
       <c r="N11" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O11" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="12" spans="8:8" ht="60.0">
+    <row r="12" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>375</v>
       </c>
@@ -2440,7 +2437,7 @@
         <v>376</v>
       </c>
       <c r="C12" s="12">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>371</v>
@@ -2449,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>369</v>
@@ -2473,13 +2470,13 @@
         <v>4</v>
       </c>
       <c r="N12" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O12" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="13" spans="8:8" ht="60.0">
+    <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>375</v>
       </c>
@@ -2487,7 +2484,7 @@
         <v>376</v>
       </c>
       <c r="C13" s="12">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>371</v>
@@ -2496,7 +2493,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>369</v>
@@ -2520,13 +2517,13 @@
         <v>4</v>
       </c>
       <c r="N13" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O13" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="14" spans="8:8" ht="60.0">
+    <row r="14" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>375</v>
       </c>
@@ -2534,7 +2531,7 @@
         <v>376</v>
       </c>
       <c r="C14" s="7">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>371</v>
@@ -2543,7 +2540,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>369</v>
@@ -2567,13 +2564,13 @@
         <v>2</v>
       </c>
       <c r="N14" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O14" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="15" spans="8:8" ht="60.0">
+    <row r="15" spans="1:15" ht="45" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>375</v>
       </c>
@@ -2581,7 +2578,7 @@
         <v>376</v>
       </c>
       <c r="C15" s="12">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>371</v>
@@ -2590,7 +2587,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>369</v>
@@ -2614,13 +2611,13 @@
         <v>2</v>
       </c>
       <c r="N15" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O15" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="16" spans="8:8" ht="60.0">
+    <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>375</v>
       </c>
@@ -2628,7 +2625,7 @@
         <v>376</v>
       </c>
       <c r="C16" s="12">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>371</v>
@@ -2637,7 +2634,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>369</v>
@@ -2661,13 +2658,13 @@
         <v>3</v>
       </c>
       <c r="N16" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O16" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="17" spans="8:8" ht="60.0">
+    <row r="17" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>375</v>
       </c>
@@ -2675,7 +2672,7 @@
         <v>376</v>
       </c>
       <c r="C17" s="7">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>371</v>
@@ -2684,7 +2681,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>369</v>
@@ -2708,13 +2705,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O17" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="18" spans="8:8" ht="60.0">
+    <row r="18" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>375</v>
       </c>
@@ -2722,7 +2719,7 @@
         <v>376</v>
       </c>
       <c r="C18" s="12">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>371</v>
@@ -2731,7 +2728,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>369</v>
@@ -2755,13 +2752,13 @@
         <v>2</v>
       </c>
       <c r="N18" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O18" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="19" spans="8:8" ht="46.5" customHeight="1">
+    <row r="19" spans="1:15" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>375</v>
       </c>
@@ -2769,7 +2766,7 @@
         <v>376</v>
       </c>
       <c r="C19" s="12">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>371</v>
@@ -2778,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>369</v>
@@ -2802,13 +2799,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O19" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="20" spans="8:8" ht="60.0">
+    <row r="20" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>375</v>
       </c>
@@ -2816,7 +2813,7 @@
         <v>376</v>
       </c>
       <c r="C20" s="7">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>371</v>
@@ -2825,7 +2822,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>369</v>
@@ -2849,13 +2846,13 @@
         <v>3</v>
       </c>
       <c r="N20" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O20" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="21" spans="8:8" ht="60.0">
+    <row r="21" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>375</v>
       </c>
@@ -2863,7 +2860,7 @@
         <v>376</v>
       </c>
       <c r="C21" s="12">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>371</v>
@@ -2872,7 +2869,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>369</v>
@@ -2896,13 +2893,13 @@
         <v>3</v>
       </c>
       <c r="N21" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O21" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="22" spans="8:8" ht="60.0">
+    <row r="22" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>375</v>
       </c>
@@ -2910,7 +2907,7 @@
         <v>376</v>
       </c>
       <c r="C22" s="12">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>371</v>
@@ -2919,7 +2916,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>369</v>
@@ -2943,13 +2940,13 @@
         <v>3</v>
       </c>
       <c r="N22" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O22" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="23" spans="8:8" ht="60.0">
+    <row r="23" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>375</v>
       </c>
@@ -2957,7 +2954,7 @@
         <v>376</v>
       </c>
       <c r="C23" s="7">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>371</v>
@@ -2966,7 +2963,7 @@
         <v>3</v>
       </c>
       <c r="F23" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>369</v>
@@ -2990,13 +2987,13 @@
         <v>4</v>
       </c>
       <c r="N23" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O23" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="24" spans="8:8" ht="60.0">
+    <row r="24" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>375</v>
       </c>
@@ -3004,7 +3001,7 @@
         <v>376</v>
       </c>
       <c r="C24" s="12">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>371</v>
@@ -3013,7 +3010,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>369</v>
@@ -3037,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O24" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="25" spans="8:8" ht="60.0">
+    <row r="25" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>375</v>
       </c>
@@ -3051,7 +3048,7 @@
         <v>376</v>
       </c>
       <c r="C25" s="12">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>371</v>
@@ -3060,7 +3057,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>369</v>
@@ -3084,13 +3081,13 @@
         <v>3</v>
       </c>
       <c r="N25" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O25" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="26" spans="8:8" ht="60.0">
+    <row r="26" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>375</v>
       </c>
@@ -3098,7 +3095,7 @@
         <v>376</v>
       </c>
       <c r="C26" s="7">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>372</v>
@@ -3107,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>369</v>
@@ -3116,28 +3113,28 @@
         <v>102</v>
       </c>
       <c r="I26" s="17">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="17">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K26" s="17">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="17">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>2</v>
       </c>
       <c r="N26" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O26" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="27" spans="8:8" ht="60.0">
+    <row r="27" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>375</v>
       </c>
@@ -3145,7 +3142,7 @@
         <v>376</v>
       </c>
       <c r="C27" s="12">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>372</v>
@@ -3154,7 +3151,7 @@
         <v>3</v>
       </c>
       <c r="F27" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>369</v>
@@ -3178,13 +3175,13 @@
         <v>4</v>
       </c>
       <c r="N27" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O27" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="28" spans="8:8" ht="60.0">
+    <row r="28" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>375</v>
       </c>
@@ -3192,7 +3189,7 @@
         <v>376</v>
       </c>
       <c r="C28" s="12">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>372</v>
@@ -3201,7 +3198,7 @@
         <v>4</v>
       </c>
       <c r="F28" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>369</v>
@@ -3225,13 +3222,13 @@
         <v>2</v>
       </c>
       <c r="N28" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O28" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="29" spans="8:8" ht="60.0">
+    <row r="29" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>375</v>
       </c>
@@ -3239,7 +3236,7 @@
         <v>376</v>
       </c>
       <c r="C29" s="7">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>372</v>
@@ -3248,7 +3245,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>369</v>
@@ -3272,13 +3269,13 @@
         <v>2</v>
       </c>
       <c r="N29" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O29" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="30" spans="8:8" ht="60.0">
+    <row r="30" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>375</v>
       </c>
@@ -3286,7 +3283,7 @@
         <v>376</v>
       </c>
       <c r="C30" s="12">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>372</v>
@@ -3295,7 +3292,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>369</v>
@@ -3319,13 +3316,13 @@
         <v>4</v>
       </c>
       <c r="N30" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O30" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="31" spans="8:8" ht="60.0">
+    <row r="31" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>375</v>
       </c>
@@ -3333,7 +3330,7 @@
         <v>376</v>
       </c>
       <c r="C31" s="12">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>372</v>
@@ -3342,7 +3339,7 @@
         <v>4</v>
       </c>
       <c r="F31" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>369</v>
@@ -3366,13 +3363,13 @@
         <v>3</v>
       </c>
       <c r="N31" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O31" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="32" spans="8:8" ht="60.0">
+    <row r="32" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>375</v>
       </c>
@@ -3380,7 +3377,7 @@
         <v>376</v>
       </c>
       <c r="C32" s="7">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>372</v>
@@ -3389,7 +3386,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>369</v>
@@ -3398,13 +3395,13 @@
         <v>128</v>
       </c>
       <c r="I32" s="17">
-        <v>1310.0</v>
+        <v>1310</v>
       </c>
       <c r="J32" s="17">
-        <v>1550.0</v>
+        <v>1550</v>
       </c>
       <c r="K32" s="17">
-        <v>850.0</v>
+        <v>850</v>
       </c>
       <c r="L32" s="17" t="s">
         <v>90</v>
@@ -3413,13 +3410,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O32" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="33" spans="8:8" ht="60.0">
+    <row r="33" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>375</v>
       </c>
@@ -3427,7 +3424,7 @@
         <v>376</v>
       </c>
       <c r="C33" s="12">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>372</v>
@@ -3436,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>369</v>
@@ -3460,13 +3457,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O33" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="34" spans="8:8" ht="60.0">
+    <row r="34" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>375</v>
       </c>
@@ -3474,7 +3471,7 @@
         <v>376</v>
       </c>
       <c r="C34" s="12">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>372</v>
@@ -3483,7 +3480,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>369</v>
@@ -3507,13 +3504,13 @@
         <v>4</v>
       </c>
       <c r="N34" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O34" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="35" spans="8:8" ht="60.0">
+    <row r="35" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>375</v>
       </c>
@@ -3521,7 +3518,7 @@
         <v>376</v>
       </c>
       <c r="C35" s="7">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>372</v>
@@ -3530,7 +3527,7 @@
         <v>4</v>
       </c>
       <c r="F35" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>369</v>
@@ -3554,13 +3551,13 @@
         <v>4</v>
       </c>
       <c r="N35" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O35" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="36" spans="8:8" ht="60.0">
+    <row r="36" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>375</v>
       </c>
@@ -3568,7 +3565,7 @@
         <v>376</v>
       </c>
       <c r="C36" s="12">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>372</v>
@@ -3577,7 +3574,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>369</v>
@@ -3601,13 +3598,13 @@
         <v>4</v>
       </c>
       <c r="N36" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O36" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="37" spans="8:8" ht="60.0">
+    <row r="37" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>375</v>
       </c>
@@ -3615,7 +3612,7 @@
         <v>376</v>
       </c>
       <c r="C37" s="12">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>372</v>
@@ -3624,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>369</v>
@@ -3648,13 +3645,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="15">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O37" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="38" spans="8:8" ht="60.0">
+    <row r="38" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>375</v>
       </c>
@@ -3662,7 +3659,7 @@
         <v>376</v>
       </c>
       <c r="C38" s="7">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>372</v>
@@ -3671,7 +3668,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>369</v>
@@ -3695,13 +3692,13 @@
         <v>4</v>
       </c>
       <c r="N38" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O38" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="39" spans="8:8" ht="60.0">
+    <row r="39" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>375</v>
       </c>
@@ -3709,7 +3706,7 @@
         <v>376</v>
       </c>
       <c r="C39" s="12">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>372</v>
@@ -3718,7 +3715,7 @@
         <v>4</v>
       </c>
       <c r="F39" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>369</v>
@@ -3742,13 +3739,13 @@
         <v>2</v>
       </c>
       <c r="N39" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O39" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="40" spans="8:8" ht="60.0">
+    <row r="40" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>375</v>
       </c>
@@ -3756,7 +3753,7 @@
         <v>376</v>
       </c>
       <c r="C40" s="12">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>372</v>
@@ -3765,7 +3762,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>369</v>
@@ -3789,13 +3786,13 @@
         <v>3</v>
       </c>
       <c r="N40" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O40" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="41" spans="8:8" ht="60.0">
+    <row r="41" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>375</v>
       </c>
@@ -3803,7 +3800,7 @@
         <v>376</v>
       </c>
       <c r="C41" s="7">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>372</v>
@@ -3812,7 +3809,7 @@
         <v>3</v>
       </c>
       <c r="F41" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>369</v>
@@ -3836,13 +3833,13 @@
         <v>2</v>
       </c>
       <c r="N41" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O41" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="42" spans="8:8" ht="60.0">
+    <row r="42" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>375</v>
       </c>
@@ -3850,7 +3847,7 @@
         <v>376</v>
       </c>
       <c r="C42" s="12">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>372</v>
@@ -3859,7 +3856,7 @@
         <v>2</v>
       </c>
       <c r="F42" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>369</v>
@@ -3883,13 +3880,13 @@
         <v>4</v>
       </c>
       <c r="N42" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O42" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="43" spans="8:8" ht="60.0">
+    <row r="43" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>375</v>
       </c>
@@ -3897,7 +3894,7 @@
         <v>376</v>
       </c>
       <c r="C43" s="12">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>372</v>
@@ -3906,7 +3903,7 @@
         <v>4</v>
       </c>
       <c r="F43" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>369</v>
@@ -3930,13 +3927,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O43" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="44" spans="8:8" ht="60.0">
+    <row r="44" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>375</v>
       </c>
@@ -3944,7 +3941,7 @@
         <v>376</v>
       </c>
       <c r="C44" s="7">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>372</v>
@@ -3953,7 +3950,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G44" s="8" t="s">
         <v>369</v>
@@ -3977,13 +3974,13 @@
         <v>2</v>
       </c>
       <c r="N44" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O44" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="45" spans="8:8" ht="60.0">
+    <row r="45" spans="1:15" ht="45" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
         <v>375</v>
       </c>
@@ -3991,7 +3988,7 @@
         <v>376</v>
       </c>
       <c r="C45" s="12">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>372</v>
@@ -4000,7 +3997,7 @@
         <v>4</v>
       </c>
       <c r="F45" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>369</v>
@@ -4024,13 +4021,13 @@
         <v>1</v>
       </c>
       <c r="N45" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O45" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="46" spans="8:8" ht="60.0">
+    <row r="46" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>375</v>
       </c>
@@ -4038,7 +4035,7 @@
         <v>376</v>
       </c>
       <c r="C46" s="12">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>372</v>
@@ -4047,7 +4044,7 @@
         <v>3</v>
       </c>
       <c r="F46" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>369</v>
@@ -4071,13 +4068,13 @@
         <v>2</v>
       </c>
       <c r="N46" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O46" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="47" spans="8:8" ht="60.0">
+    <row r="47" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>375</v>
       </c>
@@ -4085,7 +4082,7 @@
         <v>376</v>
       </c>
       <c r="C47" s="7">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>372</v>
@@ -4094,7 +4091,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="8" t="s">
         <v>369</v>
@@ -4118,13 +4115,13 @@
         <v>3</v>
       </c>
       <c r="N47" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O47" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="48" spans="8:8" ht="60.0">
+    <row r="48" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
         <v>375</v>
       </c>
@@ -4132,7 +4129,7 @@
         <v>376</v>
       </c>
       <c r="C48" s="12">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>372</v>
@@ -4141,7 +4138,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G48" s="8" t="s">
         <v>369</v>
@@ -4165,13 +4162,13 @@
         <v>3</v>
       </c>
       <c r="N48" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O48" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="49" spans="8:8" ht="60.0">
+    <row r="49" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>375</v>
       </c>
@@ -4179,7 +4176,7 @@
         <v>376</v>
       </c>
       <c r="C49" s="12">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>372</v>
@@ -4188,7 +4185,7 @@
         <v>4</v>
       </c>
       <c r="F49" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>369</v>
@@ -4212,13 +4209,13 @@
         <v>4</v>
       </c>
       <c r="N49" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O49" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="50" spans="8:8" ht="60.0">
+    <row r="50" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>375</v>
       </c>
@@ -4226,7 +4223,7 @@
         <v>376</v>
       </c>
       <c r="C50" s="7">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>372</v>
@@ -4235,7 +4232,7 @@
         <v>3</v>
       </c>
       <c r="F50" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="8" t="s">
         <v>369</v>
@@ -4259,13 +4256,13 @@
         <v>1</v>
       </c>
       <c r="N50" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O50" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="51" spans="8:8" ht="60.0">
+    <row r="51" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
         <v>375</v>
       </c>
@@ -4273,7 +4270,7 @@
         <v>376</v>
       </c>
       <c r="C51" s="12">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>372</v>
@@ -4282,7 +4279,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G51" s="8" t="s">
         <v>369</v>
@@ -4306,13 +4303,13 @@
         <v>3</v>
       </c>
       <c r="N51" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O51" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="52" spans="8:8" ht="60.0">
+    <row r="52" spans="1:15" ht="45" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>375</v>
       </c>
@@ -4320,7 +4317,7 @@
         <v>376</v>
       </c>
       <c r="C52" s="12">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>372</v>
@@ -4329,7 +4326,7 @@
         <v>1</v>
       </c>
       <c r="F52" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>369</v>
@@ -4353,13 +4350,13 @@
         <v>1</v>
       </c>
       <c r="N52" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O52" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="53" spans="8:8" ht="60.0">
+    <row r="53" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
         <v>375</v>
       </c>
@@ -4367,7 +4364,7 @@
         <v>376</v>
       </c>
       <c r="C53" s="7">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>372</v>
@@ -4376,7 +4373,7 @@
         <v>4</v>
       </c>
       <c r="F53" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>369</v>
@@ -4400,13 +4397,13 @@
         <v>4</v>
       </c>
       <c r="N53" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O53" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="54" spans="8:8" ht="60.0">
+    <row r="54" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>375</v>
       </c>
@@ -4414,7 +4411,7 @@
         <v>376</v>
       </c>
       <c r="C54" s="12">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>372</v>
@@ -4423,7 +4420,7 @@
         <v>2</v>
       </c>
       <c r="F54" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>369</v>
@@ -4447,13 +4444,13 @@
         <v>4</v>
       </c>
       <c r="N54" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O54" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="55" spans="8:8" ht="60.0">
+    <row r="55" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
         <v>375</v>
       </c>
@@ -4461,7 +4458,7 @@
         <v>376</v>
       </c>
       <c r="C55" s="12">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>372</v>
@@ -4470,7 +4467,7 @@
         <v>3</v>
       </c>
       <c r="F55" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>369</v>
@@ -4494,13 +4491,13 @@
         <v>3</v>
       </c>
       <c r="N55" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O55" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="56" spans="8:8" ht="60.0">
+    <row r="56" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>375</v>
       </c>
@@ -4508,7 +4505,7 @@
         <v>376</v>
       </c>
       <c r="C56" s="7">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>373</v>
@@ -4517,7 +4514,7 @@
         <v>1</v>
       </c>
       <c r="F56" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G56" s="8" t="s">
         <v>369</v>
@@ -4541,13 +4538,13 @@
         <v>4</v>
       </c>
       <c r="N56" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O56" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="57" spans="8:8" ht="60.0">
+    <row r="57" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>375</v>
       </c>
@@ -4555,7 +4552,7 @@
         <v>376</v>
       </c>
       <c r="C57" s="12">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>373</v>
@@ -4564,7 +4561,7 @@
         <v>4</v>
       </c>
       <c r="F57" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>369</v>
@@ -4588,13 +4585,13 @@
         <v>4</v>
       </c>
       <c r="N57" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O57" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="58" spans="8:8" ht="60.0">
+    <row r="58" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
         <v>375</v>
       </c>
@@ -4602,7 +4599,7 @@
         <v>376</v>
       </c>
       <c r="C58" s="12">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>373</v>
@@ -4611,7 +4608,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="8" t="s">
         <v>369</v>
@@ -4635,13 +4632,13 @@
         <v>3</v>
       </c>
       <c r="N58" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O58" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="59" spans="8:8" ht="60.0">
+    <row r="59" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>375</v>
       </c>
@@ -4649,7 +4646,7 @@
         <v>376</v>
       </c>
       <c r="C59" s="7">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>373</v>
@@ -4658,7 +4655,7 @@
         <v>3</v>
       </c>
       <c r="F59" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="8" t="s">
         <v>369</v>
@@ -4682,13 +4679,13 @@
         <v>4</v>
       </c>
       <c r="N59" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O59" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="60" spans="8:8" ht="60.0">
+    <row r="60" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
         <v>375</v>
       </c>
@@ -4696,7 +4693,7 @@
         <v>376</v>
       </c>
       <c r="C60" s="12">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>373</v>
@@ -4705,7 +4702,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G60" s="8" t="s">
         <v>369</v>
@@ -4714,28 +4711,28 @@
         <v>217</v>
       </c>
       <c r="I60" s="12">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="J60" s="12">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="K60" s="12">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="L60" s="12">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="M60" s="12" t="s">
         <v>4</v>
       </c>
       <c r="N60" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O60" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="61" spans="8:8" ht="60.0">
+    <row r="61" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
         <v>375</v>
       </c>
@@ -4743,7 +4740,7 @@
         <v>376</v>
       </c>
       <c r="C61" s="12">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>373</v>
@@ -4752,7 +4749,7 @@
         <v>4</v>
       </c>
       <c r="F61" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="8" t="s">
         <v>369</v>
@@ -4776,13 +4773,13 @@
         <v>1</v>
       </c>
       <c r="N61" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O61" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="62" spans="8:8" ht="60.0">
+    <row r="62" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
         <v>375</v>
       </c>
@@ -4790,7 +4787,7 @@
         <v>376</v>
       </c>
       <c r="C62" s="7">
-        <v>61.0</v>
+        <v>61</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>373</v>
@@ -4799,7 +4796,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="8" t="s">
         <v>369</v>
@@ -4817,19 +4814,19 @@
         <v>0.99</v>
       </c>
       <c r="L62" s="22">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="21" t="s">
         <v>3</v>
       </c>
       <c r="N62" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O62" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="63" spans="8:8" ht="60.0">
+    <row r="63" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
         <v>375</v>
       </c>
@@ -4837,7 +4834,7 @@
         <v>376</v>
       </c>
       <c r="C63" s="12">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>373</v>
@@ -4846,7 +4843,7 @@
         <v>3</v>
       </c>
       <c r="F63" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>369</v>
@@ -4870,13 +4867,13 @@
         <v>4</v>
       </c>
       <c r="N63" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O63" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="64" spans="8:8" ht="60.0">
+    <row r="64" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
         <v>375</v>
       </c>
@@ -4884,7 +4881,7 @@
         <v>376</v>
       </c>
       <c r="C64" s="12">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>373</v>
@@ -4893,7 +4890,7 @@
         <v>1</v>
       </c>
       <c r="F64" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G64" s="8" t="s">
         <v>369</v>
@@ -4917,13 +4914,13 @@
         <v>4</v>
       </c>
       <c r="N64" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O64" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="65" spans="8:8" ht="60.0">
+    <row r="65" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
         <v>375</v>
       </c>
@@ -4931,7 +4928,7 @@
         <v>376</v>
       </c>
       <c r="C65" s="7">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="D65" s="7" t="s">
         <v>373</v>
@@ -4940,7 +4937,7 @@
         <v>4</v>
       </c>
       <c r="F65" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G65" s="8" t="s">
         <v>369</v>
@@ -4964,13 +4961,13 @@
         <v>2</v>
       </c>
       <c r="N65" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O65" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="66" spans="8:8" ht="60.0">
+    <row r="66" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
         <v>375</v>
       </c>
@@ -4978,7 +4975,7 @@
         <v>376</v>
       </c>
       <c r="C66" s="12">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>373</v>
@@ -4987,7 +4984,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G66" s="8" t="s">
         <v>369</v>
@@ -5011,13 +5008,13 @@
         <v>2</v>
       </c>
       <c r="N66" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O66" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="67" spans="8:8" ht="60.0">
+    <row r="67" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
         <v>375</v>
       </c>
@@ -5025,7 +5022,7 @@
         <v>376</v>
       </c>
       <c r="C67" s="12">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>373</v>
@@ -5034,7 +5031,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G67" s="8" t="s">
         <v>369</v>
@@ -5058,13 +5055,13 @@
         <v>4</v>
       </c>
       <c r="N67" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O67" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="68" spans="8:8" ht="60.0">
+    <row r="68" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
         <v>375</v>
       </c>
@@ -5072,7 +5069,7 @@
         <v>376</v>
       </c>
       <c r="C68" s="7">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>373</v>
@@ -5081,7 +5078,7 @@
         <v>3</v>
       </c>
       <c r="F68" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G68" s="8" t="s">
         <v>369</v>
@@ -5105,13 +5102,13 @@
         <v>4</v>
       </c>
       <c r="N68" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O68" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="69" spans="8:8" ht="60.0">
+    <row r="69" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
         <v>375</v>
       </c>
@@ -5119,7 +5116,7 @@
         <v>376</v>
       </c>
       <c r="C69" s="12">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="D69" s="7" t="s">
         <v>373</v>
@@ -5128,7 +5125,7 @@
         <v>4</v>
       </c>
       <c r="F69" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G69" s="8" t="s">
         <v>369</v>
@@ -5152,13 +5149,13 @@
         <v>3</v>
       </c>
       <c r="N69" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O69" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="70" spans="8:8" ht="60.0">
+    <row r="70" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
         <v>375</v>
       </c>
@@ -5166,7 +5163,7 @@
         <v>376</v>
       </c>
       <c r="C70" s="12">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>373</v>
@@ -5175,7 +5172,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G70" s="8" t="s">
         <v>369</v>
@@ -5199,13 +5196,13 @@
         <v>4</v>
       </c>
       <c r="N70" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O70" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="71" spans="8:8" ht="60.0">
+    <row r="71" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
         <v>375</v>
       </c>
@@ -5213,7 +5210,7 @@
         <v>376</v>
       </c>
       <c r="C71" s="7">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>373</v>
@@ -5222,7 +5219,7 @@
         <v>3</v>
       </c>
       <c r="F71" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G71" s="8" t="s">
         <v>369</v>
@@ -5246,13 +5243,13 @@
         <v>3</v>
       </c>
       <c r="N71" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O71" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="72" spans="8:8" ht="60.0">
+    <row r="72" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
         <v>375</v>
       </c>
@@ -5260,7 +5257,7 @@
         <v>376</v>
       </c>
       <c r="C72" s="12">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="D72" s="7" t="s">
         <v>373</v>
@@ -5269,7 +5266,7 @@
         <v>3</v>
       </c>
       <c r="F72" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G72" s="8" t="s">
         <v>369</v>
@@ -5293,13 +5290,13 @@
         <v>2</v>
       </c>
       <c r="N72" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O72" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="73" spans="8:8" ht="60.0">
+    <row r="73" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
         <v>375</v>
       </c>
@@ -5307,7 +5304,7 @@
         <v>376</v>
       </c>
       <c r="C73" s="12">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="D73" s="7" t="s">
         <v>373</v>
@@ -5316,7 +5313,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="8" t="s">
         <v>383</v>
@@ -5336,13 +5333,13 @@
         <v>438</v>
       </c>
       <c r="N73" s="15">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O73" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="74" spans="8:8" ht="60.0">
+    <row r="74" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
         <v>375</v>
       </c>
@@ -5350,7 +5347,7 @@
         <v>376</v>
       </c>
       <c r="C74" s="7">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>373</v>
@@ -5359,7 +5356,7 @@
         <v>3</v>
       </c>
       <c r="F74" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G74" s="8" t="s">
         <v>369</v>
@@ -5383,13 +5380,13 @@
         <v>4</v>
       </c>
       <c r="N74" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O74" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="75" spans="8:8" ht="60.0">
+    <row r="75" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
         <v>375</v>
       </c>
@@ -5397,7 +5394,7 @@
         <v>376</v>
       </c>
       <c r="C75" s="12">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>373</v>
@@ -5406,7 +5403,7 @@
         <v>2</v>
       </c>
       <c r="F75" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G75" s="8" t="s">
         <v>369</v>
@@ -5430,13 +5427,13 @@
         <v>3</v>
       </c>
       <c r="N75" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O75" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="76" spans="8:8" ht="60.0">
+    <row r="76" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
         <v>375</v>
       </c>
@@ -5444,7 +5441,7 @@
         <v>376</v>
       </c>
       <c r="C76" s="12">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="D76" s="7" t="s">
         <v>373</v>
@@ -5453,7 +5450,7 @@
         <v>3</v>
       </c>
       <c r="F76" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G76" s="8" t="s">
         <v>369</v>
@@ -5477,13 +5474,13 @@
         <v>2</v>
       </c>
       <c r="N76" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O76" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="77" spans="8:8" ht="60.0">
+    <row r="77" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
         <v>375</v>
       </c>
@@ -5491,7 +5488,7 @@
         <v>376</v>
       </c>
       <c r="C77" s="7">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>373</v>
@@ -5500,7 +5497,7 @@
         <v>2</v>
       </c>
       <c r="F77" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G77" s="8" t="s">
         <v>369</v>
@@ -5524,13 +5521,13 @@
         <v>1</v>
       </c>
       <c r="N77" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O77" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="78" spans="8:8" ht="60.0">
+    <row r="78" spans="1:15" ht="45" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
         <v>375</v>
       </c>
@@ -5538,7 +5535,7 @@
         <v>376</v>
       </c>
       <c r="C78" s="12">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="D78" s="7" t="s">
         <v>373</v>
@@ -5547,7 +5544,7 @@
         <v>4</v>
       </c>
       <c r="F78" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G78" s="8" t="s">
         <v>369</v>
@@ -5571,13 +5568,13 @@
         <v>2</v>
       </c>
       <c r="N78" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O78" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="79" spans="8:8" ht="60.0">
+    <row r="79" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
         <v>375</v>
       </c>
@@ -5585,7 +5582,7 @@
         <v>376</v>
       </c>
       <c r="C79" s="12">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>373</v>
@@ -5594,7 +5591,7 @@
         <v>3</v>
       </c>
       <c r="F79" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G79" s="8" t="s">
         <v>369</v>
@@ -5618,13 +5615,13 @@
         <v>1</v>
       </c>
       <c r="N79" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O79" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="80" spans="8:8" ht="60.0">
+    <row r="80" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A80" s="6" t="s">
         <v>375</v>
       </c>
@@ -5632,7 +5629,7 @@
         <v>376</v>
       </c>
       <c r="C80" s="7">
-        <v>79.0</v>
+        <v>79</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>373</v>
@@ -5641,7 +5638,7 @@
         <v>2</v>
       </c>
       <c r="F80" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="8" t="s">
         <v>369</v>
@@ -5665,13 +5662,13 @@
         <v>3</v>
       </c>
       <c r="N80" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O80" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="81" spans="8:8" ht="60.0">
+    <row r="81" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
         <v>375</v>
       </c>
@@ -5679,7 +5676,7 @@
         <v>376</v>
       </c>
       <c r="C81" s="12">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="D81" s="7" t="s">
         <v>373</v>
@@ -5688,7 +5685,7 @@
         <v>3</v>
       </c>
       <c r="F81" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G81" s="8" t="s">
         <v>369</v>
@@ -5712,13 +5709,13 @@
         <v>3</v>
       </c>
       <c r="N81" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O81" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="82" spans="8:8" ht="60.0">
+    <row r="82" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A82" s="6" t="s">
         <v>375</v>
       </c>
@@ -5726,7 +5723,7 @@
         <v>376</v>
       </c>
       <c r="C82" s="12">
-        <v>81.0</v>
+        <v>81</v>
       </c>
       <c r="D82" s="7" t="s">
         <v>373</v>
@@ -5735,7 +5732,7 @@
         <v>3</v>
       </c>
       <c r="F82" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G82" s="8" t="s">
         <v>369</v>
@@ -5759,13 +5756,13 @@
         <v>1</v>
       </c>
       <c r="N82" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O82" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="83" spans="8:8" ht="60.0">
+    <row r="83" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
         <v>375</v>
       </c>
@@ -5773,7 +5770,7 @@
         <v>376</v>
       </c>
       <c r="C83" s="7">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>373</v>
@@ -5782,7 +5779,7 @@
         <v>4</v>
       </c>
       <c r="F83" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G83" s="8" t="s">
         <v>369</v>
@@ -5806,13 +5803,13 @@
         <v>4</v>
       </c>
       <c r="N83" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O83" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="84" spans="8:8" ht="60.0">
+    <row r="84" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A84" s="6" t="s">
         <v>375</v>
       </c>
@@ -5820,7 +5817,7 @@
         <v>376</v>
       </c>
       <c r="C84" s="12">
-        <v>83.0</v>
+        <v>83</v>
       </c>
       <c r="D84" s="7" t="s">
         <v>373</v>
@@ -5829,7 +5826,7 @@
         <v>3</v>
       </c>
       <c r="F84" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G84" s="8" t="s">
         <v>369</v>
@@ -5853,13 +5850,13 @@
         <v>2</v>
       </c>
       <c r="N84" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O84" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="85" spans="8:8" ht="60.0">
+    <row r="85" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
         <v>375</v>
       </c>
@@ -5867,7 +5864,7 @@
         <v>376</v>
       </c>
       <c r="C85" s="12">
-        <v>84.0</v>
+        <v>84</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>373</v>
@@ -5876,7 +5873,7 @@
         <v>3</v>
       </c>
       <c r="F85" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G85" s="8" t="s">
         <v>369</v>
@@ -5885,28 +5882,28 @@
         <v>312</v>
       </c>
       <c r="I85" s="12">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="J85" s="12">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="K85" s="12">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="L85" s="12">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M85" s="12" t="s">
         <v>3</v>
       </c>
       <c r="N85" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O85" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="86" spans="8:8" ht="60.0">
+    <row r="86" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
         <v>375</v>
       </c>
@@ -5914,7 +5911,7 @@
         <v>376</v>
       </c>
       <c r="C86" s="7">
-        <v>85.0</v>
+        <v>85</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>373</v>
@@ -5923,7 +5920,7 @@
         <v>4</v>
       </c>
       <c r="F86" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G86" s="8" t="s">
         <v>369</v>
@@ -5947,13 +5944,13 @@
         <v>2</v>
       </c>
       <c r="N86" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O86" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="87" spans="8:8" ht="60.0">
+    <row r="87" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A87" s="6" t="s">
         <v>375</v>
       </c>
@@ -5961,7 +5958,7 @@
         <v>376</v>
       </c>
       <c r="C87" s="12">
-        <v>86.0</v>
+        <v>86</v>
       </c>
       <c r="D87" s="7" t="s">
         <v>373</v>
@@ -5970,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G87" s="8" t="s">
         <v>369</v>
@@ -5979,28 +5976,28 @@
         <v>318</v>
       </c>
       <c r="I87" s="12">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J87" s="12">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K87" s="12">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="L87" s="12">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="M87" s="12">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="N87" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O87" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="88" spans="8:8" ht="60.0">
+    <row r="88" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A88" s="6" t="s">
         <v>375</v>
       </c>
@@ -6008,7 +6005,7 @@
         <v>376</v>
       </c>
       <c r="C88" s="12">
-        <v>87.0</v>
+        <v>87</v>
       </c>
       <c r="D88" s="7" t="s">
         <v>373</v>
@@ -6017,7 +6014,7 @@
         <v>4</v>
       </c>
       <c r="F88" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G88" s="8" t="s">
         <v>369</v>
@@ -6026,28 +6023,28 @@
         <v>319</v>
       </c>
       <c r="I88" s="12">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="J88" s="12">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K88" s="12">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="L88" s="12">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="M88" s="12">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="N88" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O88" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="89" spans="8:8" ht="60.0">
+    <row r="89" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
         <v>375</v>
       </c>
@@ -6055,7 +6052,7 @@
         <v>376</v>
       </c>
       <c r="C89" s="7">
-        <v>88.0</v>
+        <v>88</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>373</v>
@@ -6064,7 +6061,7 @@
         <v>2</v>
       </c>
       <c r="F89" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G89" s="8" t="s">
         <v>369</v>
@@ -6088,13 +6085,13 @@
         <v>1</v>
       </c>
       <c r="N89" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O89" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="90" spans="8:8" ht="60.0">
+    <row r="90" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A90" s="6" t="s">
         <v>375</v>
       </c>
@@ -6102,7 +6099,7 @@
         <v>376</v>
       </c>
       <c r="C90" s="12">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="D90" s="7" t="s">
         <v>373</v>
@@ -6111,7 +6108,7 @@
         <v>3</v>
       </c>
       <c r="F90" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G90" s="8" t="s">
         <v>369</v>
@@ -6135,13 +6132,13 @@
         <v>3</v>
       </c>
       <c r="N90" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O90" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="91" spans="8:8" ht="60.0">
+    <row r="91" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A91" s="6" t="s">
         <v>375</v>
       </c>
@@ -6149,7 +6146,7 @@
         <v>376</v>
       </c>
       <c r="C91" s="12">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="D91" s="7" t="s">
         <v>373</v>
@@ -6158,7 +6155,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G91" s="8" t="s">
         <v>369</v>
@@ -6182,13 +6179,13 @@
         <v>2</v>
       </c>
       <c r="N91" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O91" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="92" spans="8:8" ht="60.0">
+    <row r="92" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A92" s="6" t="s">
         <v>375</v>
       </c>
@@ -6196,7 +6193,7 @@
         <v>376</v>
       </c>
       <c r="C92" s="7">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="D92" s="7" t="s">
         <v>373</v>
@@ -6205,7 +6202,7 @@
         <v>4</v>
       </c>
       <c r="F92" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G92" s="8" t="s">
         <v>369</v>
@@ -6229,13 +6226,13 @@
         <v>3</v>
       </c>
       <c r="N92" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O92" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="93" spans="8:8" ht="60.0">
+    <row r="93" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A93" s="6" t="s">
         <v>375</v>
       </c>
@@ -6243,7 +6240,7 @@
         <v>376</v>
       </c>
       <c r="C93" s="12">
-        <v>92.0</v>
+        <v>92</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>373</v>
@@ -6252,7 +6249,7 @@
         <v>3</v>
       </c>
       <c r="F93" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G93" s="8" t="s">
         <v>369</v>
@@ -6276,13 +6273,13 @@
         <v>3</v>
       </c>
       <c r="N93" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O93" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="94" spans="8:8" ht="60.0">
+    <row r="94" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A94" s="6" t="s">
         <v>375</v>
       </c>
@@ -6290,7 +6287,7 @@
         <v>376</v>
       </c>
       <c r="C94" s="12">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>373</v>
@@ -6299,7 +6296,7 @@
         <v>2</v>
       </c>
       <c r="F94" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G94" s="8" t="s">
         <v>369</v>
@@ -6323,13 +6320,13 @@
         <v>1</v>
       </c>
       <c r="N94" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O94" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="95" spans="8:8" ht="60.0">
+    <row r="95" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
         <v>375</v>
       </c>
@@ -6337,7 +6334,7 @@
         <v>376</v>
       </c>
       <c r="C95" s="7">
-        <v>94.0</v>
+        <v>94</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>373</v>
@@ -6346,7 +6343,7 @@
         <v>4</v>
       </c>
       <c r="F95" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G95" s="8" t="s">
         <v>369</v>
@@ -6370,13 +6367,13 @@
         <v>2</v>
       </c>
       <c r="N95" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O95" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="96" spans="8:8" ht="60.0">
+    <row r="96" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A96" s="6" t="s">
         <v>375</v>
       </c>
@@ -6384,7 +6381,7 @@
         <v>376</v>
       </c>
       <c r="C96" s="12">
-        <v>95.0</v>
+        <v>95</v>
       </c>
       <c r="D96" s="7" t="s">
         <v>374</v>
@@ -6393,7 +6390,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G96" s="8" t="s">
         <v>369</v>
@@ -6417,13 +6414,13 @@
         <v>3</v>
       </c>
       <c r="N96" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O96" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="97" spans="8:8" ht="60.0">
+    <row r="97" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A97" s="6" t="s">
         <v>375</v>
       </c>
@@ -6431,7 +6428,7 @@
         <v>376</v>
       </c>
       <c r="C97" s="12">
-        <v>96.0</v>
+        <v>96</v>
       </c>
       <c r="D97" s="7" t="s">
         <v>374</v>
@@ -6440,7 +6437,7 @@
         <v>3</v>
       </c>
       <c r="F97" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G97" s="8" t="s">
         <v>369</v>
@@ -6464,13 +6461,13 @@
         <v>4</v>
       </c>
       <c r="N97" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O97" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="98" spans="8:8" ht="60.0">
+    <row r="98" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A98" s="6" t="s">
         <v>375</v>
       </c>
@@ -6478,7 +6475,7 @@
         <v>376</v>
       </c>
       <c r="C98" s="7">
-        <v>97.0</v>
+        <v>97</v>
       </c>
       <c r="D98" s="7" t="s">
         <v>374</v>
@@ -6487,7 +6484,7 @@
         <v>3</v>
       </c>
       <c r="F98" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G98" s="8" t="s">
         <v>369</v>
@@ -6511,13 +6508,13 @@
         <v>1</v>
       </c>
       <c r="N98" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O98" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="99" spans="8:8" ht="60.0">
+    <row r="99" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A99" s="6" t="s">
         <v>375</v>
       </c>
@@ -6525,7 +6522,7 @@
         <v>376</v>
       </c>
       <c r="C99" s="12">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>374</v>
@@ -6534,7 +6531,7 @@
         <v>2</v>
       </c>
       <c r="F99" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G99" s="8" t="s">
         <v>369</v>
@@ -6558,13 +6555,13 @@
         <v>4</v>
       </c>
       <c r="N99" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O99" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="100" spans="8:8" ht="60.0">
+    <row r="100" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A100" s="6" t="s">
         <v>375</v>
       </c>
@@ -6572,7 +6569,7 @@
         <v>376</v>
       </c>
       <c r="C100" s="12">
-        <v>99.0</v>
+        <v>99</v>
       </c>
       <c r="D100" s="7" t="s">
         <v>374</v>
@@ -6581,7 +6578,7 @@
         <v>4</v>
       </c>
       <c r="F100" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G100" s="8" t="s">
         <v>369</v>
@@ -6605,13 +6602,13 @@
         <v>1</v>
       </c>
       <c r="N100" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O100" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="101" spans="8:8" ht="60.0">
+    <row r="101" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A101" s="6" t="s">
         <v>375</v>
       </c>
@@ -6619,7 +6616,7 @@
         <v>376</v>
       </c>
       <c r="C101" s="7">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D101" s="7" t="s">
         <v>374</v>
@@ -6628,7 +6625,7 @@
         <v>1</v>
       </c>
       <c r="F101" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G101" s="8" t="s">
         <v>369</v>
@@ -6652,13 +6649,13 @@
         <v>4</v>
       </c>
       <c r="N101" s="15">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O101" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="102" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="102" spans="1:15" s="25" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A102" s="6" t="s">
         <v>375</v>
       </c>
@@ -6666,7 +6663,7 @@
         <v>376</v>
       </c>
       <c r="C102" s="7">
-        <v>101.0</v>
+        <v>101</v>
       </c>
       <c r="D102" s="26" t="s">
         <v>377</v>
@@ -6675,7 +6672,7 @@
         <v>2</v>
       </c>
       <c r="F102" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G102" s="26" t="s">
         <v>369</v>
@@ -6699,13 +6696,13 @@
         <v>1</v>
       </c>
       <c r="N102" s="26">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O102" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="103" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="103" spans="1:15" s="25" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A103" s="6" t="s">
         <v>375</v>
       </c>
@@ -6713,7 +6710,7 @@
         <v>376</v>
       </c>
       <c r="C103" s="7">
-        <v>102.0</v>
+        <v>102</v>
       </c>
       <c r="D103" s="26" t="s">
         <v>377</v>
@@ -6722,7 +6719,7 @@
         <v>4</v>
       </c>
       <c r="F103" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G103" s="26" t="s">
         <v>383</v>
@@ -6742,13 +6739,13 @@
         <v>439</v>
       </c>
       <c r="N103" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O103" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="104" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="104" spans="1:15" s="25" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A104" s="6" t="s">
         <v>375</v>
       </c>
@@ -6756,7 +6753,7 @@
         <v>376</v>
       </c>
       <c r="C104" s="7">
-        <v>103.0</v>
+        <v>103</v>
       </c>
       <c r="D104" s="26" t="s">
         <v>385</v>
@@ -6765,7 +6762,7 @@
         <v>3</v>
       </c>
       <c r="F104" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G104" s="26" t="s">
         <v>383</v>
@@ -6785,13 +6782,13 @@
         <v>439</v>
       </c>
       <c r="N104" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O104" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="105" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="105" spans="1:15" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="A105" s="6" t="s">
         <v>375</v>
       </c>
@@ -6799,7 +6796,7 @@
         <v>376</v>
       </c>
       <c r="C105" s="7">
-        <v>104.0</v>
+        <v>104</v>
       </c>
       <c r="D105" s="26" t="s">
         <v>385</v>
@@ -6808,7 +6805,7 @@
         <v>3</v>
       </c>
       <c r="F105" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G105" s="26" t="s">
         <v>369</v>
@@ -6832,13 +6829,13 @@
         <v>3</v>
       </c>
       <c r="N105" s="26">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O105" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="106" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="106" spans="1:15" s="25" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A106" s="6" t="s">
         <v>375</v>
       </c>
@@ -6846,7 +6843,7 @@
         <v>376</v>
       </c>
       <c r="C106" s="7">
-        <v>105.0</v>
+        <v>105</v>
       </c>
       <c r="D106" s="26" t="s">
         <v>392</v>
@@ -6855,7 +6852,7 @@
         <v>2</v>
       </c>
       <c r="F106" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G106" s="26" t="s">
         <v>369</v>
@@ -6879,13 +6876,13 @@
         <v>3</v>
       </c>
       <c r="N106" s="26">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O106" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="107" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="107" spans="1:15" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
         <v>375</v>
       </c>
@@ -6893,7 +6890,7 @@
         <v>376</v>
       </c>
       <c r="C107" s="7">
-        <v>106.0</v>
+        <v>106</v>
       </c>
       <c r="D107" s="26" t="s">
         <v>392</v>
@@ -6902,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="F107" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G107" s="26" t="s">
         <v>369</v>
@@ -6926,13 +6923,13 @@
         <v>4</v>
       </c>
       <c r="N107" s="26">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O107" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="108" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="108" spans="1:15" s="25" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A108" s="6" t="s">
         <v>375</v>
       </c>
@@ -6940,7 +6937,7 @@
         <v>376</v>
       </c>
       <c r="C108" s="7">
-        <v>107.0</v>
+        <v>107</v>
       </c>
       <c r="D108" s="26" t="s">
         <v>403</v>
@@ -6949,7 +6946,7 @@
         <v>3</v>
       </c>
       <c r="F108" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G108" s="26" t="s">
         <v>383</v>
@@ -6969,13 +6966,13 @@
         <v>439</v>
       </c>
       <c r="N108" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O108" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="109" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="109" spans="1:15" s="25" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A109" s="6" t="s">
         <v>375</v>
       </c>
@@ -6983,7 +6980,7 @@
         <v>376</v>
       </c>
       <c r="C109" s="7">
-        <v>108.0</v>
+        <v>108</v>
       </c>
       <c r="D109" s="26" t="s">
         <v>403</v>
@@ -6992,7 +6989,7 @@
         <v>2</v>
       </c>
       <c r="F109" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G109" s="26" t="s">
         <v>369</v>
@@ -7016,13 +7013,13 @@
         <v>2</v>
       </c>
       <c r="N109" s="26">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O109" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="110" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="110" spans="1:15" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
         <v>375</v>
       </c>
@@ -7030,7 +7027,7 @@
         <v>376</v>
       </c>
       <c r="C110" s="7">
-        <v>109.0</v>
+        <v>109</v>
       </c>
       <c r="D110" s="26" t="s">
         <v>403</v>
@@ -7039,7 +7036,7 @@
         <v>3</v>
       </c>
       <c r="F110" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G110" s="26" t="s">
         <v>369</v>
@@ -7063,13 +7060,13 @@
         <v>4</v>
       </c>
       <c r="N110" s="26">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O110" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="111" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="111" spans="1:15" s="25" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A111" s="6" t="s">
         <v>375</v>
       </c>
@@ -7077,7 +7074,7 @@
         <v>376</v>
       </c>
       <c r="C111" s="7">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="D111" s="26" t="s">
         <v>415</v>
@@ -7086,7 +7083,7 @@
         <v>4</v>
       </c>
       <c r="F111" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G111" s="26" t="s">
         <v>369</v>
@@ -7110,13 +7107,13 @@
         <v>4</v>
       </c>
       <c r="N111" s="26">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O111" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="112" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="112" spans="1:15" s="25" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
         <v>375</v>
       </c>
@@ -7124,7 +7121,7 @@
         <v>376</v>
       </c>
       <c r="C112" s="7">
-        <v>111.0</v>
+        <v>111</v>
       </c>
       <c r="D112" s="26" t="s">
         <v>415</v>
@@ -7133,7 +7130,7 @@
         <v>2</v>
       </c>
       <c r="F112" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G112" s="26" t="s">
         <v>383</v>
@@ -7153,13 +7150,13 @@
         <v>439</v>
       </c>
       <c r="N112" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O112" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="113" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="113" spans="1:15" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
         <v>375</v>
       </c>
@@ -7167,7 +7164,7 @@
         <v>376</v>
       </c>
       <c r="C113" s="7">
-        <v>112.0</v>
+        <v>112</v>
       </c>
       <c r="D113" s="26" t="s">
         <v>415</v>
@@ -7176,7 +7173,7 @@
         <v>3</v>
       </c>
       <c r="F113" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G113" s="26" t="s">
         <v>369</v>
@@ -7200,13 +7197,13 @@
         <v>2</v>
       </c>
       <c r="N113" s="26">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O113" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="114" spans="8:8" s="25" ht="60.0" customFormat="1">
+    <row r="114" spans="1:15" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="A114" s="6" t="s">
         <v>375</v>
       </c>
@@ -7214,7 +7211,7 @@
         <v>376</v>
       </c>
       <c r="C114" s="7">
-        <v>113.0</v>
+        <v>113</v>
       </c>
       <c r="D114" s="26" t="s">
         <v>415</v>
@@ -7223,7 +7220,7 @@
         <v>2</v>
       </c>
       <c r="F114" s="26">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G114" s="26" t="s">
         <v>369</v>
@@ -7247,48 +7244,48 @@
         <v>2</v>
       </c>
       <c r="N114" s="26">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O114" s="26" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="132" spans="8:8">
+    <row r="132" spans="5:15" x14ac:dyDescent="0.15">
       <c r="E132" s="28"/>
       <c r="F132" s="28"/>
       <c r="G132" s="28"/>
       <c r="N132" s="28"/>
       <c r="O132" s="28"/>
     </row>
-    <row r="151" spans="8:8">
+    <row r="151" spans="5:15" x14ac:dyDescent="0.15">
       <c r="E151" s="28"/>
       <c r="F151" s="28"/>
       <c r="G151" s="28"/>
       <c r="N151" s="28"/>
       <c r="O151" s="28"/>
     </row>
-    <row r="158" spans="8:8">
+    <row r="158" spans="5:15" x14ac:dyDescent="0.15">
       <c r="E158" s="28"/>
       <c r="F158" s="28"/>
       <c r="G158" s="28"/>
       <c r="N158" s="28"/>
       <c r="O158" s="28"/>
     </row>
-    <row r="163" spans="8:8">
+    <row r="163" spans="5:15" x14ac:dyDescent="0.15">
       <c r="E163" s="28"/>
       <c r="F163" s="28"/>
       <c r="G163" s="28"/>
       <c r="N163" s="28"/>
       <c r="O163" s="28"/>
     </row>
-    <row r="192" spans="8:8">
+    <row r="192" spans="5:15" x14ac:dyDescent="0.15">
       <c r="E192" s="28"/>
       <c r="F192" s="28"/>
       <c r="G192" s="28"/>
       <c r="N192" s="28"/>
       <c r="O192" s="28"/>
     </row>
-    <row r="230" spans="8:8">
+    <row r="230" spans="5:15" x14ac:dyDescent="0.15">
       <c r="E230" s="28"/>
       <c r="F230" s="28"/>
       <c r="G230" s="28"/>
@@ -7297,12 +7294,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1">
-    <cfRule type="duplicateValues" priority="3" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="1"/>
-    <cfRule type="duplicateValues" priority="1" dxfId="2"/>
-    <cfRule type="duplicateValues" priority="5" dxfId="3"/>
-    <cfRule type="duplicateValues" priority="4" dxfId="4"/>
-    <cfRule type="duplicateValues" priority="6" dxfId="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
